--- a/Excel_files/neveu_2023.xlsx
+++ b/Excel_files/neveu_2023.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\udickman\pySNNAP\Excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{933AEFF2-C1BE-4D8F-A90A-2D7332385368}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0395A92A-647E-40FD-AC2B-F946368CA3E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30450" yWindow="1650" windowWidth="21600" windowHeight="11175" tabRatio="816" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="816" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Neu" sheetId="3" r:id="rId1"/>
